--- a/Test/pd/fail-issue-name.xlsx
+++ b/Test/pd/fail-issue-name.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PD-SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,11 +478,6 @@
           <t>01.00</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -545,7 +540,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,7 +602,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -671,7 +664,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -722,7 +714,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -785,7 +776,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
